--- a/assets/constructions/examples/ctd_inserts_threading.xlsx
+++ b/assets/constructions/examples/ctd_inserts_threading.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:BD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,11 +684,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2ER14NPTVM7</t>
+          <t>2UI3.0TR-2TMVBX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -698,12 +723,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>U Style</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VAR_1/4</t>
+          <t>VAR_1/4U</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -713,7 +738,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -732,7 +757,7 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -742,25 +767,21 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2ER14NPT...</t>
+          <t>2UI3.0TR-2TM...</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2ER14NPT</t>
+          <t>2UI3.0TR-2TM</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>60</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
@@ -770,22 +791,16 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>EXT</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.33</v>
-      </c>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>NPT60</t>
+          <t>TP30</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -793,7 +808,7 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
@@ -801,7 +816,7 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>VARGUS_1/4ER</t>
+          <t>VARGUS_1/4UI_TMC</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -811,12 +826,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>VM7</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -845,31 +860,42 @@
           <t>2018/VARGUS2018-ENGweb</t>
         </is>
       </c>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>1800.06</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3ER3.0TRVKX</t>
+          <t>16 IR 14.0 NPTF PH6920</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VAR_3/8</t>
-        </is>
-      </c>
+          <t>PALBIT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -889,42 +915,32 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>16</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>10</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3ER3.0TR...</t>
+          <t>16IR14.0NPTF</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3ER3.0TR</t>
+          <t>16IR14.0NPTF</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>30</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
@@ -933,18 +949,18 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>EXT</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>14</v>
+      </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
-        <v>1.75</v>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>TP30</t>
+          <t>NPTF60</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -960,7 +976,7 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>VARGUS_3/8ER</t>
+          <t>PALB_16IR</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -970,12 +986,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>VKX</t>
+          <t>PH6920</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>TiN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1001,14 +1017,33 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2018/VARGUS2018-ENGweb</t>
+          <t>2022/ основной каталог Palbit</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>2226.63</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3VEL2.0ISOVK2P</t>
+          <t>3EL0.75ISOVM7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1018,7 +1053,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Slim Throat</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1033,7 +1068,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -1047,9 +1082,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>16</v>
       </c>
@@ -1064,12 +1097,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3VEL2.0ISO...</t>
+          <t>3EL0.75ISO...</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>3VEL2.0ISO</t>
+          <t>3EL0.75ISO</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -1078,13 +1111,13 @@
         <v>60</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
@@ -1100,7 +1133,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>0.46</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
@@ -1121,7 +1154,7 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>VARGUS_3/8VEL</t>
+          <t>VARGUS_3/8EL</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1131,17 +1164,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>VK2P</t>
+          <t>VM7</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
@@ -1165,11 +1198,30 @@
           <t>2018/VARGUS2018-ENGweb</t>
         </is>
       </c>
+      <c r="AZ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>1308.22</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VGD3.0ISO1.75RH-RS VPG</t>
+          <t>R41E5UNTMVTX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1179,12 +1231,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VG-Cut</t>
+          <t>Standard MiTM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VAR_VGD_3</t>
+          <t>VAR_41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1199,38 +1251,36 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>21.9</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>VGD3.0ISO1.75RH</t>
+          <t>R41E5UNTM...</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>VGD3.0ISO1.75RH-RS</t>
+          <t>R41E5UNTM</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -1239,15 +1289,9 @@
         <v>60</v>
       </c>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.75</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
           <t>F</t>
@@ -1258,33 +1302,33 @@
           <t>EXT</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5</v>
+      </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>M60</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1</v>
-      </c>
+          <t>NJ60</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AK5" t="b">
-        <v>0</v>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>VARGUS_VGD:3</t>
+          <t>VARGUS_41N</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1294,7 +1338,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>VPG</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1325,39 +1369,58 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>2018/VARGUS2018-ENGweb</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>11592.84</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3ER32W TN6025</t>
+          <t>3ER2.5TRVRX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ER/L-W</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E/I_03</t>
+          <t>VAR_3/8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PMKNS</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1372,7 +1435,9 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>16</v>
+      </c>
       <c r="N6" t="n">
         <v>10</v>
       </c>
@@ -1384,26 +1449,28 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ER32W</t>
+          <t>3ER2.5TR...</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3ER32W</t>
+          <t>3ER2.5TR</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X6" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.5</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1415,22 +1482,18 @@
           <t>EXT</t>
         </is>
       </c>
-      <c r="AB6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>WH55</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
+          <t>TP30</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
@@ -1438,14 +1501,12 @@
           <t>R</t>
         </is>
       </c>
-      <c r="AK6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>WIDIA_E/I_03</t>
+          <t>VARGUS_3/8ER</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1455,12 +1516,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>TN6025</t>
+          <t>VRX</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>TIALN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1486,7 +1547,26 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2020 / WIDIA Turning Catalogue</t>
+          <t>2018/VARGUS2018-ENGweb</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>1452.55</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
